--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,18 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -209,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -225,36 +200,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -281,7 +226,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -290,22 +235,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -328,7 +258,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -338,17 +268,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -362,18 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -807,13 +716,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -904,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -915,13 +824,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -933,10 +842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -974,7 +883,7 @@
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1033,7 +942,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1041,28 +950,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1073,31 +982,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K3" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="I3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K3" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1130,11 +1039,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1144,7 +1053,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1156,49 +1065,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1209,7 +1118,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1218,31 +1127,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1259,40 +1168,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1309,7 +1218,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1318,31 +1227,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1359,7 +1268,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1368,37 +1277,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="P5" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1409,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1418,37 +1327,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>66</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1459,7 +1368,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1468,22 +1377,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1497,8 +1406,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="5" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1509,7 +1418,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1518,137 +1427,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="6" t="s">
-        <x:v>73</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="6" t="s">
-        <x:v>73</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -120,7 +120,7 @@
     <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
-    <x:t>Server is not running
+    <x:t xml:space="preserve">
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
@@ -137,15 +137,10 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">The command could not be loaded, possibly because:
-  * You intended to execute a .NET application:
-      The application '/apps/Server/Project11.dll' does not exist.
-  * You intended to execute a .NET SDK command:
-      No .NET SDKs were found.
-Download a .NET SDK:
-https://aka.ms/dotnet/download
-Learn about SDK resolution:
-https://aka.ms/dotnet/sdk-not-found
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
 </x:t>
   </x:si>
   <x:si>
@@ -239,6 +234,12 @@
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
+    <x:t>ACK, FIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>PARTIAL</x:t>
   </x:si>
   <x:si>
@@ -246,6 +247,9 @@
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -959,13 +963,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="56.424911" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1067,13 +1071,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -1085,10 +1089,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S3" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1147,49 +1151,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1200,7 +1204,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1209,31 +1213,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="M2" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1250,7 +1254,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1259,31 +1263,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="L3" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1300,7 +1304,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1309,31 +1313,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
+      <x:c r="L4" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1350,7 +1354,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1359,31 +1363,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M5" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
         <x:v>20</x:v>
@@ -1400,7 +1404,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1409,31 +1413,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1450,7 +1454,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1459,22 +1463,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1500,7 +1504,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1509,37 +1513,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1547,7 +1551,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1574,22 +1578,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P9" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1597,7 +1601,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1624,22 +1628,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -225,28 +225,25 @@
     <x:t>ACK, PSH</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACK, RST</x:t>
   </x:si>
   <x:si>
     <x:t>Connection reset (RST) - Error occurred</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK, FIN</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>RST</x:t>
@@ -276,7 +273,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -291,11 +288,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -323,7 +315,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -339,11 +331,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -365,10 +354,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1125,7 +1110,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P10"/>
+  <x:dimension ref="A1:P12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1431,19 +1416,19 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1478,7 +1463,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1528,22 +1513,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="5" t="s">
-        <x:v>72</x:v>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:16">
@@ -1551,7 +1536,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1592,8 +1577,8 @@
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="6" t="s">
-        <x:v>74</x:v>
+      <x:c r="P9" s="5" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:16">
@@ -1601,7 +1586,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1628,10 +1613,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>59</x:v>
@@ -1642,8 +1627,108 @@
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="6" t="s">
+      <x:c r="P10" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
         <x:v>74</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="5" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,13 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -204,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -220,33 +200,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, PSH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, RST</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK, FIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -273,7 +226,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -282,17 +235,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -315,7 +258,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -325,14 +268,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -346,14 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -787,13 +716,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -884,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -895,13 +824,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -913,10 +842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -948,13 +877,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1013,7 +942,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1021,28 +950,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1053,7 +982,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1074,10 +1003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1110,11 +1039,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P12"/>
+  <x:dimension ref="A1:P8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1124,7 +1053,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1136,49 +1065,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1189,7 +1118,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1198,31 +1127,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1239,40 +1168,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1289,7 +1218,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1298,31 +1227,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1339,7 +1268,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1348,34 +1277,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1389,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1398,22 +1327,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1427,8 +1356,8 @@
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P6" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1439,7 +1368,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1448,22 +1377,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1477,8 +1406,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1489,7 +1418,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1498,22 +1427,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1527,208 +1456,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="5" t="s">
-        <x:v>69</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:16">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="5" t="s">
-        <x:v>69</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,22 +92,38 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server is not running
+Enter operation (format as A X B):</x:t>
+  </x:si>
+  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -121,6 +137,13 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -181,25 +204,37 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection established</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection established</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PSH, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Data transfer in progress</x:t>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset (RST) - Error occurred</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -226,7 +261,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -235,7 +270,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -258,7 +303,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -268,8 +313,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -283,6 +334,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -716,13 +775,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -813,7 +872,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -824,13 +883,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -842,10 +901,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -877,13 +936,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -942,7 +1001,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -950,16 +1009,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -971,7 +1030,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -982,7 +1041,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1003,10 +1062,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1039,11 +1098,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P8"/>
+  <x:dimension ref="A1:P11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1053,7 +1112,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1065,49 +1124,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1118,7 +1177,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1127,31 +1186,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1168,7 +1227,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1177,31 +1236,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1218,7 +1277,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1227,31 +1286,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1268,7 +1327,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1277,34 +1336,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1318,7 +1377,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1327,31 +1386,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1368,7 +1427,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1377,22 +1436,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1406,8 +1465,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P7" s="4" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1418,7 +1477,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1427,37 +1486,187 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:16">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="L9" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="M9" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="5" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:16">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="5" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server is not running
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -137,13 +121,6 @@
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -204,6 +181,9 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -220,21 +200,6 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset (RST) - Error occurred</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -261,7 +226,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -270,17 +235,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -303,7 +258,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -313,14 +268,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -334,14 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -775,13 +716,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -872,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -883,13 +824,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -901,10 +842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -936,13 +877,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -1001,7 +942,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -1009,28 +950,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1041,7 +982,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1062,10 +1003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1098,11 +1039,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P11"/>
+  <x:dimension ref="A1:P8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1112,7 +1053,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="35.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1124,49 +1065,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1177,7 +1118,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1186,31 +1127,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1227,40 +1168,40 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1277,7 +1218,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1286,31 +1227,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1327,7 +1268,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1336,34 +1277,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1377,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1386,31 +1327,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
@@ -1427,7 +1368,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1436,22 +1377,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1465,8 +1406,8 @@
       <x:c r="O7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>29</x:v>
+      <x:c r="P7" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1477,7 +1418,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1486,22 +1427,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1515,158 +1456,8 @@
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:16">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="5" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:16">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="5" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:16">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="5" t="s">
-        <x:v>68</x:v>
+      <x:c r="P8" s="3" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,22 +92,38 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+Enter operation (format as A X B):</x:t>
+  </x:si>
+  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -119,6 +135,13 @@
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
   </x:si>
   <x:si>
     <x:t>Time</x:t>
@@ -716,13 +739,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -813,7 +836,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -824,13 +847,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -842,10 +865,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -877,13 +900,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -942,7 +965,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -950,16 +973,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>0</x:v>
@@ -971,7 +994,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -982,7 +1005,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1003,10 +1026,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="S3" s="2" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1065,49 +1088,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1118,7 +1141,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1127,22 +1150,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
         <x:v>17</x:v>
@@ -1157,7 +1180,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
@@ -1168,7 +1191,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1177,22 +1200,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1207,7 +1230,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
@@ -1218,7 +1241,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1227,22 +1250,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1257,7 +1280,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:16">
@@ -1268,7 +1291,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1277,22 +1300,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="J5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1307,7 +1330,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1318,7 +1341,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1327,22 +1350,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1357,7 +1380,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1368,7 +1391,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1377,22 +1400,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1407,7 +1430,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1418,7 +1441,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1427,22 +1450,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1457,7 +1480,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,38 +92,22 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NONE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: client output matches exactly</x:t>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPARE_FAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OutputMismatch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison failed: client output mismatch</x:t>
   </x:si>
   <x:si>
     <x:t>3
 Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">
-Enter operation (format as A X B):</x:t>
-  </x:si>
-  <x:si>
     <x:t>ServerStdout</x:t>
   </x:si>
   <x:si>
@@ -135,13 +119,6 @@
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison passed: server output matches exactly</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Waiting for a connection from client
-</x:t>
   </x:si>
   <x:si>
     <x:t>Time</x:t>
@@ -739,13 +716,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -836,7 +813,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -847,13 +824,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>0</x:v>
@@ -865,10 +842,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -900,13 +877,13 @@
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -965,7 +942,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="S1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:19">
@@ -973,28 +950,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="I2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="0" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
         <x:v>17</x:v>
@@ -1005,7 +982,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1026,10 +1003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="S3" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1088,49 +1065,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="M1" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="N1" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="O1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="P1" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L1" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M1" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="N1" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="O1" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="P1" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1141,7 +1118,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1150,22 +1127,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
         <x:v>17</x:v>
@@ -1180,7 +1157,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16">
@@ -1191,31 +1168,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1230,7 +1207,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P3" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:16">
@@ -1241,7 +1218,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1250,22 +1227,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1280,7 +1257,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:16">
@@ -1291,7 +1268,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1300,22 +1277,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1330,7 +1307,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:16">
@@ -1341,7 +1318,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1350,22 +1327,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1380,7 +1357,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1391,7 +1368,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1400,22 +1377,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1430,7 +1407,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P7" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1441,7 +1418,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1450,22 +1427,22 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J8" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1480,7 +1457,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
+++ b/Submit/Results/dongnvhe172649/TC3_ReqResNotC/GradeDetail.xlsx
@@ -92,16 +92,16 @@
     <x:t>Enter operation (format as A X B):</x:t>
   </x:si>
   <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPARE_FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OutputMismatch</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Text comparison failed: client output mismatch</x:t>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NONE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Text comparison passed: client output matches exactly</x:t>
   </x:si>
   <x:si>
     <x:t>3
@@ -115,12 +115,21 @@
 Client disconnected</x:t>
   </x:si>
   <x:si>
-    <x:t>Text comparison failed: server output mismatch</x:t>
+    <x:t>Text comparison passed: server output matches exactly</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Client connected
+Client disconnected
+</x:t>
   </x:si>
   <x:si>
     <x:t>Waiting for a connection from client</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Waiting for a connection from client
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>Time</x:t>
   </x:si>
   <x:si>
@@ -181,9 +190,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
     <x:t>SYN, ACK</x:t>
   </x:si>
   <x:si>
@@ -200,6 +206,24 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Closing connection (FIN-ACK)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -226,7 +250,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -235,7 +259,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -258,7 +292,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -268,8 +302,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -283,6 +323,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -710,19 +758,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.282054" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.139196" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -813,7 +861,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -844,8 +892,8 @@
       <x:c r="M3" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="S3" s="2" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -871,19 +919,19 @@
     <x:col min="4" max="4" width="9.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="6.424911" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="6.282054" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.567768" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.567768" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.996339" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="11.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="43.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="50.853482" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="8.853482" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="15.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="13.139196" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="15.567768" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="13.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:19" s="1" customFormat="1">
@@ -973,8 +1021,8 @@
       <x:c r="M2" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="S2" s="2" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:19">
@@ -982,7 +1030,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>24</x:v>
@@ -1005,8 +1053,8 @@
       <x:c r="M3" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="S3" s="2" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1039,11 +1087,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P8"/>
+  <x:dimension ref="A1:P19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1052,8 +1100,8 @@
     <x:col min="8" max="8" width="4.996339" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1065,49 +1113,49 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:16">
@@ -1118,7 +1166,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>17</x:v>
@@ -1127,31 +1175,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
+      <x:c r="L2" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
@@ -1168,7 +1216,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>17</x:v>
@@ -1177,31 +1225,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K3" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
         <x:v>17</x:v>
@@ -1218,7 +1266,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>17</x:v>
@@ -1227,31 +1275,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
@@ -1268,7 +1316,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>17</x:v>
@@ -1277,34 +1325,34 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="P5" s="3" t="s">
         <x:v>24</x:v>
@@ -1318,7 +1366,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>17</x:v>
@@ -1327,37 +1375,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="P6" s="4" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:16">
@@ -1368,7 +1416,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>17</x:v>
@@ -1377,37 +1425,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="P7" s="4" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:16">
@@ -1418,7 +1466,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>17</x:v>
@@ -1427,37 +1475,587 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:16">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:16">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="M10" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:16">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="3" t="s">
-        <x:v>24</x:v>
+      <x:c r="L11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:16">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="P12" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:16">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:16">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="P14" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:16">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P15" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:16">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:16">
+      <x:c r="A17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:16">
+      <x:c r="A18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:16">
+      <x:c r="A19" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K19" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L19" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M19" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="N19" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="O19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P19" s="5" t="s">
+        <x:v>63</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
